--- a/artfynd/A 18703-2020 artfynd.xlsx
+++ b/artfynd/A 18703-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -889,6 +889,555 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>114936336</v>
+      </c>
+      <c r="B4" t="n">
+        <v>5182</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Rövarkulen, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>500420</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6345279</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bäckaby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-02-26</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-02-26</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anna-Stina Duerden</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anna-Stina Duerden</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>114936404</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79507</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Rövarkulen, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>500340</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6345412</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bäckaby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-02-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-02-26</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anna-Stina Duerden</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anna-Stina Duerden</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>114936367</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78456</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Rövarkulen, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>500377</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6345345</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bäckaby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-02-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-02-26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anna-Stina Duerden</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anna-Stina Duerden</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>114936089</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93959</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rövarkulen, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>500355</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6345405</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bäckaby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-02-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-02-26</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anna-Stina Duerden</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anna-Stina Duerden, Ricarda Schultz</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>114936194</v>
+      </c>
+      <c r="B8" t="n">
+        <v>4760</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Rövarkulen, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>500355</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6345405</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bäckaby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-02-26</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-02-26</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anna-Stina Duerden</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anna-Stina Duerden, Ricarda Schultz</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
